--- a/SeleniumTests/TestDataFolder/UserTestDataValid.xlsx
+++ b/SeleniumTests/TestDataFolder/UserTestDataValid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF307D33-4D79-4975-A230-F6CB07F24DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD103FF-6AC8-455D-AD48-6465F67FAB1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31155" yWindow="990" windowWidth="21600" windowHeight="11235" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateUserRoleTestData" sheetId="2" r:id="rId1"/>
@@ -31,44 +31,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="30">
   <si>
     <t>true</t>
   </si>
   <si>
-    <t>Rolename</t>
-  </si>
-  <si>
-    <t>RoleDesc</t>
-  </si>
-  <si>
-    <t>colorClass</t>
-  </si>
-  <si>
-    <t>EditStorePermission</t>
-  </si>
-  <si>
     <t>badge-info</t>
   </si>
   <si>
     <t>Username</t>
   </si>
   <si>
-    <t>CustEmail</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>UserPassword</t>
-  </si>
-  <si>
-    <t>UserConfirmPassword</t>
-  </si>
-  <si>
-    <t>activeUser</t>
-  </si>
-  <si>
     <t>Admin</t>
   </si>
   <si>
@@ -118,6 +91,36 @@
   </si>
   <si>
     <t>testing3@qubeapps.com</t>
+  </si>
+  <si>
+    <t>User Role Name</t>
+  </si>
+  <si>
+    <t>User Role Description</t>
+  </si>
+  <si>
+    <t>Color Class</t>
+  </si>
+  <si>
+    <t>Edit Store Permission</t>
+  </si>
+  <si>
+    <t>User Email</t>
+  </si>
+  <si>
+    <t>User Role</t>
+  </si>
+  <si>
+    <t>User Password</t>
+  </si>
+  <si>
+    <t>User Confirm Password</t>
+  </si>
+  <si>
+    <t>Active User (true/false)</t>
+  </si>
+  <si>
+    <t>Search Text</t>
   </si>
 </sst>
 </file>
@@ -450,30 +453,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{427008FF-FF76-4B05-9188-D4DB61EAACC6}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>0</v>
@@ -488,30 +497,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D2A6FA0-E17C-489F-A648-CE339D354332}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>0</v>
@@ -529,39 +544,39 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
@@ -582,24 +597,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -614,48 +629,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5097C69D-8655-4203-ACF4-F99FF3A15FF1}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>0</v>
@@ -676,24 +700,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -708,12 +732,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
